--- a/weekly-summary-abc/weekly_report.xlsx
+++ b/weekly-summary-abc/weekly_report.xlsx
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Набор кастрюль премиум 5 предметов</t>
+          <t>Универсальный обезжириватель кухни 750мл</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Сковорода керамическая 28см</t>
+          <t>Чистящее средство для духовки и плиты 500мл</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Набор бокалов универсал 6шт</t>
+          <t>Средство для мытья окон и зеркал 750мл</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>ABC-GLS-012 (Набор бокалов универсал 6шт) — падение выручки</t>
+          <t>ABC-GLS-012 (Средство для мытья окон и зеркал 750мл) — падение выручки</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
